--- a/Mechanism_Dictionary.xlsx
+++ b/Mechanism_Dictionary.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Categories" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mechanisms'!$A$1:$G$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mechanisms'!$A$1:$G$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -108,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -153,6 +153,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -520,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2324,8 +2327,89 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>M-ROT-12</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>ROT</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>Trail Leg Drive Opens The Pelvis Early.</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>트레일 다리의 추진이 골반을 조기에 연다.</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="inlineStr">
+        <is>
+          <t>Trail Leg Push Early
+Trail Leg Push Excessive</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>pelvis_open_early
+pelvis_rotation_excessive</t>
+        </is>
+      </c>
+      <c r="G51" s="16" t="inlineStr">
+        <is>
+          <t>P6 리팩토링 중 신규 등록 (2026-07-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>M-ROT-13</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>ROT</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>Body Rotation Leads The Downswing.</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>몸통 회전이 다운스윙을 주도한다.</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>Body Rotation Dominant
+Upper Body Dominance
+Body-Led Downswing</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>pelvis_open_early
+thorax_open_early
+thorax_rotation_excessive
+pelvis_rotation_excessive</t>
+        </is>
+      </c>
+      <c r="G52" s="16" t="inlineStr">
+        <is>
+          <t>P6 리팩토링 중 신규 등록 (2026-07-07). Upper Body Dominance 폐기 통합.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G50"/>
+  <autoFilter ref="A1:G52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
